--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.8-information-security-in-project-management/WKBK/90_workbooks/ISMS-IMP-A.5.8.3_Portfolio_Dashboard_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.8-information-security-in-project-management/WKBK/90_workbooks/ISMS-IMP-A.5.8.3_Portfolio_Dashboard_20260208.xlsx
@@ -5315,7 +5315,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PCI DSS</t>
+          <t>PCI DSS v4.0.1</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
